--- a/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
+++ b/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
@@ -1917,7 +1917,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_verify_started_list_fields</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="8" t="inlineStr">

--- a/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
+++ b/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
@@ -1969,7 +1969,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_verify_pagination</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="98" customHeight="1">
       <c r="A17" s="5" t="inlineStr">

--- a/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
+++ b/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
@@ -2026,7 +2026,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_start_and_stop_project</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -2389,7 +2393,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_start_and_stop_project</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="8" t="inlineStr">

--- a/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
+++ b/docs/测试用例/rfp-测试用例-签约管理-签约菜单-UI自动化.xlsx
@@ -2187,7 +2187,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_void_project</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -2235,7 +2239,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I21" s="13" t="n"/>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>tests/operate/rfp_management/test_rfp_contract_list.py-TestRFPContractList.test_void_project_cancel</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
